--- a/data/trans_bre/P37-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P37-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 3,35</t>
+          <t>-8,23; 2,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 6,03</t>
+          <t>-6,48; 6,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 7,56</t>
+          <t>-4,84; 7,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 14,66</t>
+          <t>0,14; 14,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-46,98; 30,88</t>
+          <t>-48,02; 26,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-35,52; 44,82</t>
+          <t>-32,64; 50,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-28,62; 65,43</t>
+          <t>-27,37; 65,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 62,75</t>
+          <t>0,44; 60,09</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 6,49</t>
+          <t>-1,7; 6,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 4,7</t>
+          <t>-5,41; 4,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 2,31</t>
+          <t>-7,02; 2,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 10,07</t>
+          <t>-1,65; 9,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-15,0; 75,86</t>
+          <t>-14,5; 78,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-26,75; 33,7</t>
+          <t>-26,4; 34,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-38,78; 17,21</t>
+          <t>-38,76; 18,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 44,09</t>
+          <t>-5,67; 42,67</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 9,43</t>
+          <t>-2,07; 9,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 3,97</t>
+          <t>-8,43; 4,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 8,74</t>
+          <t>-3,59; 9,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 9,61</t>
+          <t>-2,54; 9,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,37; 76,67</t>
+          <t>-12,51; 82,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-33,95; 23,29</t>
+          <t>-35,03; 24,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-16,36; 55,41</t>
+          <t>-16,34; 56,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 39,51</t>
+          <t>-8,52; 39,78</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 9,33</t>
+          <t>-0,44; 9,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 12,05</t>
+          <t>-0,85; 11,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 8,02</t>
+          <t>-4,16; 7,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-18,38; 5,18</t>
+          <t>-15,4; 6,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 95,17</t>
+          <t>-3,22; 100,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 83,36</t>
+          <t>-4,42; 74,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-16,36; 51,6</t>
+          <t>-18,93; 44,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-50,55; 16,46</t>
+          <t>-43,82; 21,05</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 12,0</t>
+          <t>-3,51; 11,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 10,02</t>
+          <t>-6,1; 10,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 7,05</t>
+          <t>-5,94; 6,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 14,19</t>
+          <t>0,19; 14,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-16,36; 101,86</t>
+          <t>-19,48; 98,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-26,12; 84,85</t>
+          <t>-27,54; 75,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-36,92; 73,01</t>
+          <t>-36,82; 68,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 51,44</t>
+          <t>0,4; 52,88</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 10,45</t>
+          <t>-1,47; 10,76</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 8,53</t>
+          <t>-4,83; 8,72</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 11,33</t>
+          <t>-2,78; 11,16</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,19; 16,84</t>
+          <t>4,7; 16,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-8,21; 104,99</t>
+          <t>-9,63; 109,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-21,94; 50,21</t>
+          <t>-20,48; 50,08</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-15,4; 69,49</t>
+          <t>-12,22; 72,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14,39; 73,91</t>
+          <t>15,54; 70,45</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 6,0</t>
+          <t>-2,08; 6,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 3,52</t>
+          <t>-4,34; 4,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 7,48</t>
+          <t>-1,14; 7,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,77; 43,74</t>
+          <t>2,86; 45,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,31; 45,23</t>
+          <t>-12,34; 46,9</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-26,89; 23,41</t>
+          <t>-22,72; 27,29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 52,67</t>
+          <t>-6,45; 49,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,43; 152,47</t>
+          <t>8,39; 154,45</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 3,36</t>
+          <t>-3,48; 3,66</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 4,29</t>
+          <t>-3,6; 3,69</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 5,35</t>
+          <t>-1,41; 5,54</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,5; 28,84</t>
+          <t>2,84; 29,24</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-21,73; 25,2</t>
+          <t>-21,37; 27,09</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-18,89; 31,07</t>
+          <t>-19,82; 26,04</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 50,78</t>
+          <t>-10,27; 54,56</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,24; 212,54</t>
+          <t>7,17; 210,33</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,78</t>
+          <t>0,24; 3,72</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 2,44</t>
+          <t>-1,31; 2,48</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 3,46</t>
+          <t>-0,15; 3,48</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,57; 22,68</t>
+          <t>4,43; 20,9</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,02; 29,0</t>
+          <t>1,86; 29,17</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 14,79</t>
+          <t>-6,84; 15,07</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 23,56</t>
+          <t>-1,06; 23,6</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14,35; 91,46</t>
+          <t>14,03; 79,88</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P37-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P37-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,68</t>
+          <t>5,07</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>17,89%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 2,99</t>
+          <t>-8,41; 3,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 6,81</t>
+          <t>-6,55; 5,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 7,44</t>
+          <t>-4,92; 7,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 14,34</t>
+          <t>-0,94; 11,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-48,02; 26,75</t>
+          <t>-47,66; 27,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-32,64; 50,99</t>
+          <t>-32,59; 43,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-27,37; 65,29</t>
+          <t>-26,5; 64,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 60,09</t>
+          <t>-3,35; 44,93</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,36</t>
+          <t>3,23</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>11,78%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 6,18</t>
+          <t>-1,83; 6,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 4,86</t>
+          <t>-5,49; 4,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 2,38</t>
+          <t>-7,03; 1,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 9,91</t>
+          <t>-2,99; 8,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-14,5; 78,37</t>
+          <t>-15,31; 72,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-26,4; 34,94</t>
+          <t>-26,67; 29,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-38,76; 18,73</t>
+          <t>-39,26; 13,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 42,67</t>
+          <t>-9,58; 35,79</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,78</t>
+          <t>4,27</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>15,83%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 9,86</t>
+          <t>-2,2; 9,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,43; 4,24</t>
+          <t>-8,41; 4,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 9,25</t>
+          <t>-3,59; 9,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 9,69</t>
+          <t>-1,08; 10,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,51; 82,3</t>
+          <t>-13,2; 82,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-35,03; 24,74</t>
+          <t>-34,15; 26,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-16,34; 56,56</t>
+          <t>-16,28; 57,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 39,78</t>
+          <t>-3,83; 43,4</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-3,43</t>
+          <t>5,81</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-10,61%</t>
+          <t>19,86%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 9,66</t>
+          <t>-0,75; 9,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 11,17</t>
+          <t>0,15; 11,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 7,27</t>
+          <t>-3,7; 8,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,4; 6,41</t>
+          <t>-0,79; 12,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 100,54</t>
+          <t>-5,76; 100,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 74,49</t>
+          <t>0,16; 75,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-18,93; 44,74</t>
+          <t>-16,99; 50,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-43,82; 21,05</t>
+          <t>-2,37; 49,58</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,58</t>
+          <t>8,72</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>30,02%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 11,48</t>
+          <t>-3,98; 11,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 10,04</t>
+          <t>-4,39; 10,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 6,84</t>
+          <t>-5,54; 7,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 14,32</t>
+          <t>2,29; 15,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-19,48; 98,89</t>
+          <t>-20,67; 93,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-27,54; 75,79</t>
+          <t>-22,09; 80,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-36,82; 68,56</t>
+          <t>-37,53; 76,91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,4; 52,88</t>
+          <t>6,9; 64,33</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10,6</t>
+          <t>10,76</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>40,87%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 10,76</t>
+          <t>-1,37; 10,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 8,72</t>
+          <t>-5,6; 9,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 11,16</t>
+          <t>-3,63; 10,79</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,7; 16,62</t>
+          <t>4,26; 16,07</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-9,63; 109,58</t>
+          <t>-9,4; 100,95</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-20,48; 50,08</t>
+          <t>-22,12; 50,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-12,22; 72,49</t>
+          <t>-16,17; 66,52</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15,54; 70,45</t>
+          <t>13,77; 68,62</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20,06</t>
+          <t>3,67</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>11,22%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 6,19</t>
+          <t>-1,87; 6,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 4,08</t>
+          <t>-4,76; 3,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 7,24</t>
+          <t>-1,66; 7,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,86; 45,75</t>
+          <t>-1,03; 9,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,34; 46,9</t>
+          <t>-11,48; 46,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-22,72; 27,29</t>
+          <t>-24,77; 26,57</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 49,54</t>
+          <t>-8,73; 53,87</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,39; 154,45</t>
+          <t>-3,06; 30,12</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13,83</t>
+          <t>4,75</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>12,83%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 3,66</t>
+          <t>-4,09; 3,6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 3,69</t>
+          <t>-3,58; 4,03</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 5,54</t>
+          <t>-1,41; 5,46</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,84; 29,24</t>
+          <t>-0,03; 9,53</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-21,37; 27,09</t>
+          <t>-23,77; 28,06</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-19,82; 26,04</t>
+          <t>-19,84; 29,87</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-10,27; 54,56</t>
+          <t>-10,32; 53,97</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,17; 210,33</t>
+          <t>-0,07; 27,83</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10,04</t>
+          <t>5,07</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,24; 3,72</t>
+          <t>0,26; 3,74</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 2,48</t>
+          <t>-1,34; 2,57</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 3,48</t>
+          <t>-0,33; 3,45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,43; 20,9</t>
+          <t>2,8; 7,14</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,86; 29,17</t>
+          <t>1,67; 28,25</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 15,07</t>
+          <t>-7,15; 15,63</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 23,6</t>
+          <t>-1,99; 23,28</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14,03; 79,88</t>
+          <t>8,78; 24,14</t>
         </is>
       </c>
     </row>
